--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="296">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,10 +532,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -4568,7 +4571,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4587,7 +4590,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4598,8 +4601,12 @@
       <c r="K33" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+      <c r="L33" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4669,10 +4676,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4686,7 +4693,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4695,13 +4702,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4752,7 +4759,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4772,10 +4779,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4871,12 +4878,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4886,13 +4893,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -4905,7 +4912,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4917,7 +4924,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -4956,7 +4963,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4974,28 +4981,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5008,7 +5015,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5020,7 +5027,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5059,7 +5066,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5079,17 +5086,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5111,7 +5118,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5123,7 +5130,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5162,7 +5169,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5182,17 +5189,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5214,7 +5221,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5265,7 +5272,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5283,28 +5290,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5317,7 +5324,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5329,7 +5336,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5368,7 +5375,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5388,10 +5395,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5414,11 +5421,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5469,7 +5476,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5489,10 +5496,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5519,7 +5526,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5570,7 +5577,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5590,17 +5597,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5618,11 +5625,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5673,7 +5680,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5693,17 +5700,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5721,11 +5728,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5776,7 +5783,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5796,17 +5803,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5824,11 +5831,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5879,7 +5886,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5899,10 +5906,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5916,7 +5923,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5925,13 +5932,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5982,7 +5989,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6002,10 +6009,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6019,7 +6026,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6028,13 +6035,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6085,7 +6092,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6105,10 +6112,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6131,7 +6138,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6184,7 +6191,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6204,10 +6211,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6263,25 +6270,25 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6301,10 +6308,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6327,7 +6334,7 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6380,7 +6387,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6400,10 +6407,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6426,7 +6433,7 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6479,7 +6486,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6499,10 +6506,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6525,7 +6532,7 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6578,7 +6585,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6598,10 +6605,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6615,7 +6622,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6624,10 +6631,10 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -6679,7 +6686,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6699,10 +6706,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6800,10 +6807,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6901,10 +6908,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7002,10 +7009,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7103,10 +7110,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7206,10 +7213,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7309,10 +7316,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7412,10 +7419,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7515,10 +7522,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7616,10 +7623,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7649,7 +7656,7 @@
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
@@ -7675,7 +7682,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7693,7 +7700,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7713,10 +7720,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7750,7 +7757,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>74</v>
@@ -7792,7 +7799,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7812,10 +7819,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7838,7 +7845,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7891,7 +7898,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7911,10 +7918,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7937,7 +7944,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7990,7 +7997,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8010,10 +8017,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8036,7 +8043,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8089,7 +8096,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8109,10 +8116,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8135,7 +8142,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8188,7 +8195,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8208,10 +8215,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8234,7 +8241,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8287,7 +8294,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8307,10 +8314,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8333,7 +8340,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8386,7 +8393,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8406,10 +8413,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8432,7 +8439,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8485,7 +8492,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8505,10 +8512,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8531,7 +8538,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8584,7 +8591,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8604,10 +8611,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8630,7 +8637,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8683,7 +8690,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8703,10 +8710,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8729,7 +8736,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8782,7 +8789,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8802,10 +8809,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8903,10 +8910,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9004,10 +9011,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9105,10 +9112,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9206,10 +9213,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9309,10 +9316,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9412,10 +9419,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9515,10 +9522,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9618,10 +9625,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9719,10 +9726,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9749,7 +9756,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9758,7 +9765,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>74</v>
@@ -9800,7 +9807,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9820,10 +9827,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9857,7 +9864,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>74</v>
@@ -9899,7 +9906,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -9919,10 +9926,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -9945,7 +9952,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -9998,7 +10005,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-vaccinations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
